--- a/output/soil_prop_summary_table.xlsx
+++ b/output/soil_prop_summary_table.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,27 +362,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>new.ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>pH</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Water</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Bulk density</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>g/g</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>g/cm3</t>
         </is>
@@ -396,15 +401,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Trial 1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>5.95 ± 0</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.21 ± 0.01</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1.2 ± 0.13</t>
         </is>
@@ -418,15 +428,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Trial 3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>5.72 ± 0.13</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.15 ± 0.01</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.19 ± 0.01</t>
         </is>
@@ -440,15 +455,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Trial 5</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>5.61 ± 0.01</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.18 ± 0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1.06 ± 0.05</t>
         </is>
@@ -462,15 +482,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Trial 2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>5.96 ± 0.08</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.17 ± 0.01</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1.29 ± 0.09</t>
         </is>
@@ -484,15 +509,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Trial 4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>5.79 ± 0</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>0.15 ± 0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>1.15 ± 0.03</t>
         </is>
@@ -506,15 +536,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Trial 6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>6.53 ± 0.01</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>0.21 ± 0.01</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1.1 ± 0.03</t>
         </is>
@@ -528,15 +563,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Trial 7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>5.7 ± 0.01</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>0.2 ± 0.01</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1.13 ± 0.04</t>
         </is>
@@ -550,15 +590,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Trial 8</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>5.34 ± 0.01</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>0.13 ± 0.02</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>1.03 ± 0.02</t>
         </is>
@@ -572,15 +617,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Trial 9</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>5.69 ± 0.01</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>0.2 ± 0.01</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>1.37 ± 0.03</t>
         </is>

--- a/output/soil_prop_summary_table.xlsx
+++ b/output/soil_prop_summary_table.xlsx
@@ -1,21 +1,152 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aarhusuniversitet-my.sharepoint.com/personal/au583430_uni_au_dk/Documents/Documents/GitHub/Pedersen-2026-STABIL/output/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_EC7EFDCE8F79A8D366075C52F3D85A70ACBCA632" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB71B979-9290-4D2D-A807-D2B1A386A57D}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="8170" yWindow="1200" windowWidth="10870" windowHeight="8250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+  <si>
+    <t>new.ID</t>
+  </si>
+  <si>
+    <t>pH</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Bulk density</t>
+  </si>
+  <si>
+    <t>g/g</t>
+  </si>
+  <si>
+    <t>g/cm3</t>
+  </si>
+  <si>
+    <t>Trial 1</t>
+  </si>
+  <si>
+    <t>5.95 ± 0</t>
+  </si>
+  <si>
+    <t>0.21 ± 0.01</t>
+  </si>
+  <si>
+    <t>1.2 ± 0.13</t>
+  </si>
+  <si>
+    <t>Trial 3</t>
+  </si>
+  <si>
+    <t>5.72 ± 0.13</t>
+  </si>
+  <si>
+    <t>0.15 ± 0.01</t>
+  </si>
+  <si>
+    <t>1.19 ± 0.01</t>
+  </si>
+  <si>
+    <t>Trial 5</t>
+  </si>
+  <si>
+    <t>5.61 ± 0.01</t>
+  </si>
+  <si>
+    <t>0.18 ± 0</t>
+  </si>
+  <si>
+    <t>1.06 ± 0.05</t>
+  </si>
+  <si>
+    <t>Trial 2</t>
+  </si>
+  <si>
+    <t>5.96 ± 0.08</t>
+  </si>
+  <si>
+    <t>0.17 ± 0.01</t>
+  </si>
+  <si>
+    <t>1.29 ± 0.09</t>
+  </si>
+  <si>
+    <t>Trial 4</t>
+  </si>
+  <si>
+    <t>5.79 ± 0</t>
+  </si>
+  <si>
+    <t>0.15 ± 0</t>
+  </si>
+  <si>
+    <t>1.15 ± 0.03</t>
+  </si>
+  <si>
+    <t>Trial 6</t>
+  </si>
+  <si>
+    <t>6.53 ± 0.01</t>
+  </si>
+  <si>
+    <t>1.1 ± 0.03</t>
+  </si>
+  <si>
+    <t>Trial 7</t>
+  </si>
+  <si>
+    <t>5.7 ± 0.01</t>
+  </si>
+  <si>
+    <t>0.2 ± 0.01</t>
+  </si>
+  <si>
+    <t>1.13 ± 0.04</t>
+  </si>
+  <si>
+    <t>Trial 8</t>
+  </si>
+  <si>
+    <t>5.34 ± 0.01</t>
+  </si>
+  <si>
+    <t>0.13 ± 0.02</t>
+  </si>
+  <si>
+    <t>1.03 ± 0.02</t>
+  </si>
+  <si>
+    <t>Trial 9</t>
+  </si>
+  <si>
+    <t>5.69 ± 0.01</t>
+  </si>
+  <si>
+    <t>1.37 ± 0.03</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +194,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +246,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +280,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +315,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,290 +491,161 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.1796875" customWidth="1"/>
+    <col min="3" max="3" width="16.6328125" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>experiment</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>new.ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>pH</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Bulk density</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>g/g</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>g/cm3</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Trial 1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>5.95 ± 0</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.21 ± 0.01</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1.2 ± 0.13</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Trial 3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>5.72 ± 0.13</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.15 ± 0.01</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1.19 ± 0.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Trial 5</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>5.61 ± 0.01</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.18 ± 0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1.06 ± 0.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Trial 2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>5.96 ± 0.08</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.17 ± 0.01</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1.29 ± 0.09</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Trial 4</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5.79 ± 0</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.15 ± 0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1.15 ± 0.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Trial 6</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>6.53 ± 0.01</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.21 ± 0.01</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1.1 ± 0.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Trial 7</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>5.7 ± 0.01</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.2 ± 0.01</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1.13 ± 0.04</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Trial 8</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>5.34 ± 0.01</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.13 ± 0.02</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1.03 ± 0.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Trial 9</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>5.69 ± 0.01</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.2 ± 0.01</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1.37 ± 0.03</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
